--- a/prueba.xlsx
+++ b/prueba.xlsx
@@ -5,42 +5,86 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\llama\Escritorio\clasificador\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mimposervicios-my.sharepoint.com/personal/practicante2_sistemas_mimpo_com/Documents/Escritorio/clasif/clasificacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E67E99-FFBB-4D4C-AD8C-0D5A50EE9DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{37E67E99-FFBB-4D4C-AD8C-0D5A50EE9DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77FFE272-20E9-402D-922D-45CC205F9770}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
   <si>
     <t>productos</t>
   </si>
   <si>
     <t>proveedor</t>
+  </si>
+  <si>
+    <t>aa</t>
+  </si>
+  <si>
+    <t>bb</t>
+  </si>
+  <si>
+    <t>cc</t>
+  </si>
+  <si>
+    <t>dd</t>
+  </si>
+  <si>
+    <t>ee</t>
+  </si>
+  <si>
+    <t>ff</t>
+  </si>
+  <si>
+    <t>gg</t>
+  </si>
+  <si>
+    <t>hh</t>
+  </si>
+  <si>
+    <t>hp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -349,10 +393,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B5:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>0</v>
       </c>
@@ -360,67 +404,105 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10">
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B16" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17">
-        <v>90</v>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
